--- a/output/laminas_comunales/comunal_m_miginterna_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2022_valparaiso.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_miginterna_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2022_valparaiso.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: Santo Domingo (13,1); El Tabo (30,4); El Quisco (18,7); Algarrobo (20,4); Puchuncaví (17,3); Zapallar (20,7); y 1 más. Bajo umbral: Calera (-9,8).</t>
         </is>
       </c>
     </row>
